--- a/04_Continuous_no_group/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/04_Continuous_no_group/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -795,13 +795,13 @@
     <t>04_Continuous_no_group/01_Trait_Associations/01_Proteins/c_data/protein_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>6981dbb51aef4b50cb02881f1fa1e4bd</t>
+    <t>40ba0b9472959680583a47b54709babd</t>
   </si>
   <si>
     <t>04_Continuous_no_group/01_Trait_Associations/02_Sets/c_data/set_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>fc927edf38cdb65fc6e6ef7b5ee61d0b</t>
+    <t>fff7d186d73c2394eda17ac62e9ef20d</t>
   </si>
   <si>
     <t>modules</t>
@@ -810,7 +810,7 @@
     <t>04_Continuous_no_group/01_Trait_Associations/03_Modules/c_data/module_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>a390b13ecd5db17176a38fdfca27a68e</t>
+    <t>d1c9683ff404598b92cc56c90f977475</t>
   </si>
   <si>
     <t>pathways</t>
@@ -819,7 +819,7 @@
     <t>04_Continuous_no_group/02_Trait_Pathways/c_data/trait_pathways.xlsx</t>
   </si>
   <si>
-    <t>b047a6b1784d7c6972a99fec0255149c</t>
+    <t>3a1e600bd13bd7859943f9ba42d45d9f</t>
   </si>
   <si>
     <t>gene_sets</t>
@@ -828,13 +828,13 @@
     <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
-    <t>587e179734739b4ba3ccdf9a51c3f6c0</t>
+    <t>bc1bf66e89df936e164c317354990470</t>
   </si>
   <si>
     <t>04_Continuous_no_group/03_Profile_Clusters/c_data/profile_clusters.xlsx</t>
   </si>
   <si>
-    <t>1765e0af4b3672723de1077b5b9820c6</t>
+    <t>46e319363a497258db15c6c02049a6d2</t>
   </si>
   <si>
     <t>corrected</t>

--- a/04_Continuous_no_group/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/04_Continuous_no_group/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -795,13 +795,13 @@
     <t>04_Continuous_no_group/01_Trait_Associations/01_Proteins/c_data/protein_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>40ba0b9472959680583a47b54709babd</t>
+    <t>53a8d72f35199120ea36dfc0a0edd388</t>
   </si>
   <si>
     <t>04_Continuous_no_group/01_Trait_Associations/02_Sets/c_data/set_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>fff7d186d73c2394eda17ac62e9ef20d</t>
+    <t>2280a0fab813462105503234ed926188</t>
   </si>
   <si>
     <t>modules</t>
@@ -810,7 +810,7 @@
     <t>04_Continuous_no_group/01_Trait_Associations/03_Modules/c_data/module_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>d1c9683ff404598b92cc56c90f977475</t>
+    <t>606023bdde4b337ab41426882cfc5e9e</t>
   </si>
   <si>
     <t>pathways</t>
@@ -819,13 +819,13 @@
     <t>04_Continuous_no_group/02_Trait_Pathways/c_data/trait_pathways.xlsx</t>
   </si>
   <si>
-    <t>3a1e600bd13bd7859943f9ba42d45d9f</t>
+    <t>35e88a5c51acb13d1d96743d8d8c1745</t>
   </si>
   <si>
     <t>gene_sets</t>
   </si>
   <si>
-    <t>01_Trunk/04_Gene_Sets/c_data/gene_sets.rds</t>
+    <t>01_Processing/04_Gene_Sets/c_data/gene_sets.rds</t>
   </si>
   <si>
     <t>bc1bf66e89df936e164c317354990470</t>
@@ -834,13 +834,13 @@
     <t>04_Continuous_no_group/03_Profile_Clusters/c_data/profile_clusters.xlsx</t>
   </si>
   <si>
-    <t>46e319363a497258db15c6c02049a6d2</t>
+    <t>bcf87bef5a4009ff39b9274e314245c7</t>
   </si>
   <si>
     <t>corrected</t>
   </si>
   <si>
-    <t>01_Trunk/03_Quantification/c_data/DAList_corrected.rds</t>
+    <t>01_Processing/03_Quantification/c_data/DAList_corrected.rds</t>
   </si>
   <si>
     <t>4b7147a39661ba7f9ed17b81a9ef9a9b</t>

--- a/04_Continuous_no_group/Figures/F1_Overview/c_data/f1_overview.xlsx
+++ b/04_Continuous_no_group/Figures/F1_Overview/c_data/f1_overview.xlsx
@@ -795,13 +795,13 @@
     <t>04_Continuous_no_group/01_Trait_Associations/01_Proteins/c_data/protein_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>53a8d72f35199120ea36dfc0a0edd388</t>
+    <t>400e71a7f9b28b71965d7d0a160d06c9</t>
   </si>
   <si>
     <t>04_Continuous_no_group/01_Trait_Associations/02_Sets/c_data/set_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>2280a0fab813462105503234ed926188</t>
+    <t>3d21c84292f410b6f34c484bd5074e96</t>
   </si>
   <si>
     <t>modules</t>
@@ -810,7 +810,7 @@
     <t>04_Continuous_no_group/01_Trait_Associations/03_Modules/c_data/module_trait_associations.xlsx</t>
   </si>
   <si>
-    <t>606023bdde4b337ab41426882cfc5e9e</t>
+    <t>ff084ce743cbe0bc8a39fddd8f920530</t>
   </si>
   <si>
     <t>pathways</t>
@@ -819,7 +819,7 @@
     <t>04_Continuous_no_group/02_Trait_Pathways/c_data/trait_pathways.xlsx</t>
   </si>
   <si>
-    <t>35e88a5c51acb13d1d96743d8d8c1745</t>
+    <t>37b270811c8ae46c10a723e86f5256e5</t>
   </si>
   <si>
     <t>gene_sets</t>
@@ -834,7 +834,7 @@
     <t>04_Continuous_no_group/03_Profile_Clusters/c_data/profile_clusters.xlsx</t>
   </si>
   <si>
-    <t>bcf87bef5a4009ff39b9274e314245c7</t>
+    <t>e27701d11c4ee900dd3353dcc577a065</t>
   </si>
   <si>
     <t>corrected</t>
